--- a/files/九龙-旺角-The Boundary.xlsx
+++ b/files/九龙-旺角-The Boundary.xlsx
@@ -114,7 +114,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -250,7 +251,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -745,7 +746,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -755,12 +756,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -770,12 +771,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -785,7 +786,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -815,7 +816,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -825,12 +826,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -840,12 +841,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -855,7 +856,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -885,7 +886,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -895,12 +896,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -910,12 +911,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -925,7 +926,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -955,7 +956,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -965,12 +966,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -980,12 +981,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -995,7 +996,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1026,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1035,12 +1036,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1050,12 +1051,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1065,7 +1066,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1096,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1105,12 +1106,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1120,12 +1121,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1135,7 +1136,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1166,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1175,12 +1176,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1190,12 +1191,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1205,7 +1206,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1236,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1245,12 +1246,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1260,12 +1261,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1275,7 +1276,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1306,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1315,12 +1316,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1330,12 +1331,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1345,7 +1346,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1376,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1385,12 +1386,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1400,12 +1401,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1415,7 +1416,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1446,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1455,12 +1456,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1470,12 +1471,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1485,7 +1486,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1516,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1525,12 +1526,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1540,12 +1541,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1555,7 +1556,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1586,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1595,12 +1596,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1610,12 +1611,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1625,7 +1626,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1656,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1665,12 +1666,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1680,12 +1681,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1695,7 +1696,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1735,12 +1736,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1750,12 +1751,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1765,7 +1766,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1796,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1805,12 +1806,12 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1820,12 +1821,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1835,7 +1836,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1866,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1875,12 +1876,12 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1890,12 +1891,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1905,7 +1906,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1936,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -1945,12 +1946,12 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1960,12 +1961,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -1975,7 +1976,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2006,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2015,12 +2016,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2030,12 +2031,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2045,7 +2046,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2076,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2085,12 +2086,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2100,12 +2101,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2115,7 +2116,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2146,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2155,12 +2156,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2170,12 +2171,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2185,7 +2186,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2216,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2225,12 +2226,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2240,12 +2241,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2255,7 +2256,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2286,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2295,12 +2296,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2310,12 +2311,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2325,7 +2326,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2356,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2365,12 +2366,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2380,12 +2381,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2395,7 +2396,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2426,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2435,12 +2436,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2450,12 +2451,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2465,7 +2466,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2496,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2505,12 +2506,12 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2520,12 +2521,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2535,7 +2536,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2566,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2575,12 +2576,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2590,12 +2591,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2605,7 +2606,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2636,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2645,12 +2646,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2660,12 +2661,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2675,7 +2676,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2706,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -2715,12 +2716,12 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2730,12 +2731,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2745,7 +2746,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2776,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2785,12 +2786,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2800,12 +2801,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
@@ -2815,7 +2816,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2846,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2855,12 +2856,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2870,12 +2871,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2885,7 +2886,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2916,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2925,12 +2926,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2940,12 +2941,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2955,7 +2956,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2986,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2995,12 +2996,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3010,12 +3011,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3025,7 +3026,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3056,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3065,12 +3066,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -3080,12 +3081,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3095,7 +3096,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3126,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3135,12 +3136,12 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -3150,12 +3151,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -3165,7 +3166,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3196,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3205,12 +3206,12 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -3220,12 +3221,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3235,7 +3236,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3266,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3275,12 +3276,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -3290,12 +3291,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3305,7 +3306,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3336,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3345,12 +3346,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -3360,12 +3361,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3375,7 +3376,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3406,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3415,12 +3416,12 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -3430,12 +3431,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3445,7 +3446,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3476,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3485,12 +3486,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3500,12 +3501,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3515,7 +3516,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3546,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3555,12 +3556,12 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3570,12 +3571,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3585,7 +3586,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3616,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3625,12 +3626,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3640,12 +3641,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3655,7 +3656,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3686,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3695,12 +3696,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3710,12 +3711,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3725,7 +3726,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3756,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3765,12 +3766,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3780,12 +3781,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3795,7 +3796,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3826,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3835,12 +3836,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3850,12 +3851,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3865,7 +3866,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3896,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3905,12 +3906,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3920,12 +3921,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3935,7 +3936,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3966,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3975,12 +3976,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3990,12 +3991,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -4005,7 +4006,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4036,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -4045,12 +4046,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -4060,12 +4061,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4075,7 +4076,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4106,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4115,12 +4116,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -4130,12 +4131,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4145,7 +4146,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4176,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4185,12 +4186,12 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -4200,12 +4201,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4215,7 +4216,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4246,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4255,12 +4256,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -4270,12 +4271,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4285,7 +4286,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4316,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4325,12 +4326,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -4340,12 +4341,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4355,7 +4356,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4386,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4395,12 +4396,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4410,12 +4411,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4425,7 +4426,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4456,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4465,12 +4466,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -4480,12 +4481,12 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -4495,7 +4496,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4526,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4535,12 +4536,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4550,12 +4551,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4565,7 +4566,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4596,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4605,12 +4606,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4620,12 +4621,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4635,7 +4636,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4666,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4675,12 +4676,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -4690,12 +4691,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4705,7 +4706,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4736,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4745,12 +4746,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4760,12 +4761,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4775,7 +4776,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4850,27 +4851,27 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
     </row>
@@ -4905,17 +4906,17 @@
       <c r="B5" s="19" t="inlineStr">
         <is>
           <t>A | 261呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
           <t>B | 211呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr"/>
@@ -4929,17 +4930,17 @@
       <c r="B6" s="19" t="inlineStr">
         <is>
           <t>A | 261呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
           <t>B | 211呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -4953,25 +4954,25 @@
       <c r="B7" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -4984,25 +4985,25 @@
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5015,25 +5016,25 @@
       <c r="B9" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5046,25 +5047,25 @@
       <c r="B10" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5077,25 +5078,25 @@
       <c r="B11" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5108,25 +5109,25 @@
       <c r="B12" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5139,25 +5140,25 @@
       <c r="B13" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5170,25 +5171,25 @@
       <c r="B14" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5201,25 +5202,25 @@
       <c r="B15" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5232,25 +5233,25 @@
       <c r="B16" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5263,25 +5264,25 @@
       <c r="B17" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C17" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5294,25 +5295,25 @@
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5325,25 +5326,25 @@
       <c r="B19" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5356,25 +5357,25 @@
       <c r="B20" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5387,25 +5388,25 @@
       <c r="B21" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5418,25 +5419,25 @@
       <c r="B22" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5449,25 +5450,25 @@
       <c r="B23" s="19" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5480,25 +5481,25 @@
       <c r="B24" s="19" t="inlineStr">
         <is>
           <t>A | 192呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
           <t>B | 240呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
           <t>C | 187呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-旺角-The Boundary.xlsx
+++ b/files/九龙-旺角-The Boundary.xlsx
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="18">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +120,11 @@
       <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -195,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -207,6 +214,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,6 +265,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -631,7 +644,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -2286,23 +2299,19 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>3940000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>18762</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2311,12 +2320,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2326,7 +2335,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2636,23 +2645,19 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>18310</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2661,12 +2666,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2676,7 +2681,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3616,23 +3621,19 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>17308</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3641,12 +3642,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3656,7 +3657,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3686,23 +3687,19 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>16901</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3711,12 +3708,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3726,7 +3723,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4526,23 +4523,19 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>3340000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>15681</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4551,12 +4544,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4566,7 +4559,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4736,23 +4729,19 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>3068000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>15979</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4761,12 +4750,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4776,7 +4765,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4805,105 +4794,105 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>The Boundary 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 261呎 (1房)
 招标单位
@@ -4911,7 +4900,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 211呎 (开放式)
 招标单位
@@ -4919,15 +4908,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 261呎 (1房)
 招标单位
@@ -4935,7 +4924,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 211呎 (开放式)
 招标单位
@@ -4943,15 +4932,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -4959,7 +4948,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -4967,7 +4956,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -4977,12 +4966,12 @@
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -4990,7 +4979,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -4998,7 +4987,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5008,12 +4997,12 @@
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5021,7 +5010,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5029,7 +5018,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5039,12 +5028,12 @@
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5052,7 +5041,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5060,7 +5049,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5070,12 +5059,12 @@
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5083,7 +5072,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5091,7 +5080,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5101,12 +5090,12 @@
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5114,7 +5103,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5122,7 +5111,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5132,12 +5121,12 @@
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5145,7 +5134,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5153,7 +5142,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$394万
+$18,762/呎
+(26年-10月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$390万
+$18,310/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5162,13 +5182,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5176,7 +5196,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5184,7 +5204,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5193,13 +5213,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5207,7 +5227,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5215,7 +5235,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5224,13 +5244,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5238,7 +5258,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5246,7 +5266,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5255,13 +5275,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5269,7 +5289,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5277,7 +5297,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5286,13 +5306,44 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$360万
+$16,901/呎
+(26年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+$450万
+$17,308/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5300,7 +5351,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5308,7 +5359,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5317,13 +5368,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5331,7 +5382,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5339,7 +5390,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5348,13 +5399,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -5362,7 +5413,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5370,7 +5421,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5379,21 +5430,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
+$334万
+$15,681/呎
+(26年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5401,7 +5452,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5410,83 +5461,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 192呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
+$307万
+$15,979/呎
+(26年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 240呎 (1房)
 招标单位
@@ -5494,7 +5483,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 187呎 (开放式)
 招标单位

--- a/files/九龙-旺角-The Boundary.xlsx
+++ b/files/九龙-旺角-The Boundary.xlsx
@@ -3551,23 +3551,19 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>3520000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>16762</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3576,12 +3572,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3591,7 +3587,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3893,23 +3889,19 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>3590000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>16854</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3918,12 +3910,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3933,7 +3925,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3963,23 +3955,19 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>3430000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>16333</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3988,12 +3976,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -4003,7 +3991,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4103,23 +4091,19 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>16432</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4128,12 +4112,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4143,7 +4127,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4173,23 +4157,19 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>3330000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>15857</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4198,12 +4178,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4213,7 +4193,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4243,23 +4223,19 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>4270000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>16423</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4268,12 +4244,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4283,7 +4259,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4313,23 +4289,19 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>3430000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>16103</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4338,12 +4310,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4353,7 +4325,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4383,23 +4355,19 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>3290000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>15667</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4408,12 +4376,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4423,7 +4391,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4808,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4850,7 +4818,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5328,7 +5296,38 @@
 (26年-09月-29日)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$352万
+$16,762/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$359万
+$16,854/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5337,21 +5336,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+$350万
+$16,432/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5359,30 +5358,61 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+$343万
+$16,333/呎
+(26年-10月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+$343万
+$16,103/呎
+(26年-10月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+$427万
+$16,423/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$333万
+$15,857/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$334万
+$15,681/呎
+(26年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5390,74 +5420,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-$334万
-$15,681/呎
-(26年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
+$329万
+$15,667/呎
+(26年-10月-13日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-旺角-The Boundary.xlsx
+++ b/files/九龙-旺角-The Boundary.xlsx
@@ -3271,23 +3271,19 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>3780000</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>17746</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3296,12 +3292,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
@@ -3311,7 +3307,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3481,23 +3477,19 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>3680000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>17277</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3506,12 +3498,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3521,7 +3513,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3749,23 +3741,19 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>3490000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>16619</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3774,12 +3762,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3789,7 +3777,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4421,23 +4409,19 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>4240000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>16308</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4446,12 +4430,12 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -4461,7 +4445,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4557,23 +4541,19 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>18717</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4582,12 +4562,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4597,7 +4577,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4627,23 +4607,19 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>4450000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>18542</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4652,12 +4628,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4667,7 +4643,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4678,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4808,7 +4784,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4818,7 +4794,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5218,12 +5194,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
+$378万
+$17,746/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -5249,12 +5225,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
+$368万
+$17,277/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -5327,12 +5303,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
+$349万
+$16,619/呎
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5388,12 @@
 (26年-10月-03日)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
+$424万
+$16,308/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -5440,23 +5416,23 @@
           <t>A | 192呎 (开放式)
 $307万
 $15,979/呎
-(26年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 240呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
+$445万
+$18,542/呎
+(26年-10月-14日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 187呎 (开放式)
-招标单位
--
-(在售)</t>
+$350万
+$18,717/呎
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-旺角-The Boundary.xlsx
+++ b/files/九龙-旺角-The Boundary.xlsx
@@ -1529,23 +1529,19 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5330000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>20500</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1554,12 +1550,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1599,23 +1595,19 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>20188</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1624,12 +1616,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1639,7 +1631,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1879,23 +1871,19 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>4120000</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>19619</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1904,12 +1892,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -1919,7 +1907,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2019,23 +2007,19 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>4140000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>19437</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2044,12 +2028,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2059,7 +2043,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2089,23 +2073,19 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>4080000</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>19429</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2114,12 +2094,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2129,7 +2109,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2229,23 +2209,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>19249</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2254,12 +2230,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2269,7 +2245,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2435,23 +2411,19 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>3970000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>18638</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2460,12 +2432,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2475,7 +2447,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2622,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2851,23 +2823,19 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>3870000</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>18169</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2876,12 +2844,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2891,7 +2859,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3061,23 +3029,19 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>18028</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3086,12 +3050,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3101,7 +3065,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3201,23 +3165,19 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>4660000</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>17923</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3226,12 +3186,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3241,7 +3201,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3337,23 +3297,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>3610000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>17190</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3362,12 +3318,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3377,7 +3333,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3407,23 +3363,19 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>17615</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3432,12 +3384,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3447,7 +3399,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3566,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3680,7 +3632,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3807,23 +3759,19 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>4480000</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>17231</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3832,12 +3780,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3847,7 +3795,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4009,23 +3957,19 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>4370000</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>16808</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4034,12 +3978,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -4049,7 +3993,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4028,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4480,7 +4424,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4784,7 +4728,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4794,7 +4738,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4946,7 +4890,38 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$430万
+$20,188/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+$533万
+$20,500/呎
+(26年-10月-24日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 招标单位
@@ -4954,7 +4929,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -4962,7 +4937,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -4971,21 +4946,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+$414万
+$19,437/呎
+(26年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -4993,7 +4968,100 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$412万
+$19,619/呎
+(26年-10月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$410万
+$19,249/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$408万
+$19,429/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$397万
+$18,638/呎
+(26年-10月-19日)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$394万
+$18,762/呎
+(26年-10月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$390万
+$18,310/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5002,21 +5070,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+$387万
+$18,169/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5024,7 +5092,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5033,21 +5101,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
+$384万
+$18,028/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5055,7 +5123,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5064,60 +5132,29 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+$378万
+$17,746/呎
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-$394万
-$18,762/呎
-(26年-10月-04日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-$390万
-$18,310/呎
-(26年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
+$466万
+$17,923/呎
+(26年-10月-26日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5126,99 +5163,6 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-$378万
-$17,746/呎
-(26年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
@@ -5233,20 +5177,20 @@
 (26年-10月-15日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
+$458万
+$17,615/呎
+(26年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
+$361万
+$17,190/呎
+(26年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5205,7 @@
           <t>A | 213呎 (开放式)
 $360万
 $16,901/呎
-(26年-09月-30日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5269,7 +5213,7 @@
           <t>B | 260呎 (1房)
 $450万
 $17,308/呎
-(26年-09月-29日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5295,12 +5239,12 @@
 (26年-10月-12日)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
+$448万
+$17,231/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5323,15 +5267,15 @@
           <t>A | 213呎 (开放式)
 $350万
 $16,432/呎
-(26年-10月-12日)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+(26年-10月-27日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
+$437万
+$16,808/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5385,7 +5329,7 @@
           <t>A | 213呎 (开放式)
 $334万
 $15,681/呎
-(26年-10月-03日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">

--- a/files/九龙-旺角-The Boundary.xlsx
+++ b/files/九龙-旺角-The Boundary.xlsx
@@ -2477,23 +2477,19 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>3890000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>18524</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2502,12 +2498,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
@@ -2517,7 +2513,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4156,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4728,7 +4724,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -4738,7 +4734,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5061,7 +5057,38 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 210呎 (开放式)
+$389万
+$18,524/呎
+(26年-10月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 213呎 (开放式)
+$387万
+$18,169/呎
+(26年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5070,21 +5097,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-$387万
-$18,169/呎
-(26年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
+$384万
+$18,028/呎
+(26年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
 招标单位
@@ -5092,7 +5119,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5101,29 +5128,29 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
-$384万
-$18,028/呎
-(26年-10月-23日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+$378万
+$17,746/呎
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 260呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
+$466万
+$17,923/呎
+(26年-10月-26日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 210呎 (开放式)
 招标单位
@@ -5132,37 +5159,6 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>A | 213呎 (开放式)
-$378万
-$17,746/呎
-(26年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 260呎 (1房)
-$466万
-$17,923/呎
-(26年-10月-26日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 210呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
@@ -5306,7 +5302,7 @@
           <t>B | 260呎 (1房)
 $427万
 $16,423/呎
-(26年-10月-12日)</t>
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
